--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/KANSAS_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/KANSAS_2016.xlsx
@@ -2400,7 +2400,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C114">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C155">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C250">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C590">
